--- a/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1009,6 +1009,104 @@
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>97.73</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
